--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513305_ELIMINGRE12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513305_ELIMINGRE12FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4621</v>
+        <v>5.471</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8371</v>
+        <v>5.534</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625</v>
+        <v>-0.063</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3506</v>
+        <v>5.4312</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8847</v>
+        <v>8.0756</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.5341</v>
+        <v>-2.6444</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5252</v>
+        <v>7.8415</v>
       </c>
       <c r="K2" t="n">
-        <v>7.4433</v>
+        <v>7.736</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0819</v>
+        <v>0.1055</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1746</v>
+        <v>-2.4103</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4414</v>
+        <v>0.3396</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.616</v>
+        <v>-2.7499</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0079</v>
+        <v>-1.1297</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0736</v>
+        <v>0.3009</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0815</v>
+        <v>-1.4306</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4393</v>
+        <v>0.5074</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3105</v>
+        <v>4.3603</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8117</v>
+        <v>3.0235</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4989</v>
+        <v>1.3368</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8962</v>
+        <v>2.6113</v>
       </c>
       <c r="H3" t="n">
-        <v>3.491</v>
+        <v>1.616</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5948</v>
+        <v>0.9953</v>
       </c>
       <c r="J3" t="n">
-        <v>1.485</v>
+        <v>2.6177</v>
       </c>
       <c r="K3" t="n">
-        <v>2.721</v>
+        <v>2.0015</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.236</v>
+        <v>0.6163</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4112</v>
+        <v>-0.0064</v>
       </c>
       <c r="N3" t="n">
-        <v>0.77</v>
+        <v>-0.3855</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3588</v>
+        <v>0.379</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0006</v>
+        <v>2.3368</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0009</v>
+        <v>2.5316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5541</v>
+        <v>-0.5362</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4673</v>
+        <v>0.0415</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9132</v>
+        <v>-0.5778</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8597</v>
+        <v>-0.0516</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8597</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3263</v>
+        <v>3.8879</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1298</v>
+        <v>1.9547</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1964</v>
+        <v>1.9332</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5099</v>
+        <v>1.8625</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5188</v>
+        <v>3.5146</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9911</v>
+        <v>-1.6521</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3904</v>
+        <v>1.6175</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8267</v>
+        <v>2.825</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5637</v>
+        <v>-1.2074</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1195</v>
+        <v>0.2449</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3079</v>
+        <v>0.6896</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4274</v>
+        <v>-0.4446</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4007</v>
+        <v>1.9474</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2001</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6007</v>
+        <v>2.921</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.504</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.4209</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-1.2328</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0803</v>
+        <v>0.89</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5196</v>
+        <v>0.89</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8753</v>
+        <v>3.3202</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5193</v>
+        <v>2.9345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3561</v>
+        <v>0.3856</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6242</v>
+        <v>1.6455</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0469</v>
+        <v>0.0292</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5773</v>
+        <v>1.6163</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4908</v>
+        <v>2.6809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2835</v>
+        <v>0.3542</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2073</v>
+        <v>2.3267</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8666</v>
+        <v>-1.0353</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2366</v>
+        <v>-0.3249</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.63</v>
+        <v>-0.7104</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.3496</v>
+        <v>-0.8569</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0313</v>
+        <v>0.1689</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3183</v>
+        <v>-1.0258</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -877,31 +877,31 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -955,19 +955,19 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0645</v>
+        <v>0.0618</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0645</v>
+        <v>0.0618</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1046</v>
+        <v>-0.2527</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5401</v>
+        <v>0.502</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6448</v>
+        <v>-0.7546</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3949</v>
+        <v>-0.4405</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2225</v>
+        <v>0.2032</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6437</v>
       </c>
       <c r="J8" t="n">
-        <v>0.12</v>
+        <v>0.1226</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5149</v>
+        <v>-0.5631</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1425</v>
+        <v>0.1211</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6574</v>
+        <v>-0.6842</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1098</v>
+        <v>-0.2017</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4202</v>
+        <v>0.3793</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.53</v>
+        <v>-0.581</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1405</v>
+        <v>-1.3313</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9334</v>
+        <v>-0.13</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0738</v>
+        <v>-1.2014</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1704</v>
+        <v>-1.2244</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2487</v>
+        <v>-0.2679</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9218</v>
+        <v>-0.9565</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6798</v>
+        <v>0.6979</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6798</v>
+        <v>0.6979</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8502</v>
+        <v>-1.9223</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9285</v>
+        <v>-0.9658</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9218</v>
+        <v>-0.9565</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0.2047</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4539</v>
+        <v>0.3406</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1039</v>
+        <v>-0.1359</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.203</v>
+        <v>-1.3857</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4342</v>
+        <v>-1.3611</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2312</v>
+        <v>-0.0246</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0199</v>
+        <v>-1.0321</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1848</v>
+        <v>1.1658</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2046</v>
+        <v>-2.1979</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2542</v>
+        <v>-1.194</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6998</v>
+        <v>0.7184</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.954</v>
+        <v>-1.9125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2343</v>
+        <v>0.1619</v>
       </c>
       <c r="N10" t="n">
-        <v>0.485</v>
+        <v>0.4474</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9237</v>
+        <v>-1.0478</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.18</v>
+        <v>-0.167</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7437</v>
+        <v>-0.8807</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.265</v>
+        <v>-2.5084</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5329</v>
+        <v>3.5939</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.7979</v>
+        <v>-6.1023</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6018</v>
+        <v>-1.635</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6642</v>
+        <v>0.6882</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.266</v>
+        <v>-2.3231</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2852</v>
+        <v>1.3965</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6434</v>
+        <v>0.7236</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6418</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.887</v>
+        <v>-3.0315</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0207</v>
+        <v>-0.0355</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.9078</v>
+        <v>-2.996</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7226</v>
+        <v>-0.9845</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.3969</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3118</v>
+        <v>-1.3814</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8591</v>
+        <v>3.9426</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4147</v>
+        <v>-2.614</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1411</v>
+        <v>-1.3797</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2736</v>
+        <v>-1.2342</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7662</v>
+        <v>-2.8005</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5754</v>
+        <v>3.6074</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.3416</v>
+        <v>-6.4079</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5272</v>
+        <v>-0.3231</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6629</v>
+        <v>2.7968</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.19</v>
+        <v>-3.1199</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.239</v>
+        <v>-2.4774</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9125</v>
+        <v>0.8107</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.1515</v>
+        <v>-3.288</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>3.401</v>
+        <v>3.3105</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.9689</v>
+        <v>-2.0987</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5333</v>
+        <v>-0.0314</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4356</v>
+        <v>-2.0674</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7353</v>
+        <v>-7.4986</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4016</v>
+        <v>-4.9867</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3337</v>
+        <v>-2.5119</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.3279</v>
+        <v>-4.4137</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0328</v>
+        <v>-1.0792</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2952</v>
+        <v>-3.3345</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.5121</v>
+        <v>-2.4533</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.518</v>
+        <v>-0.5003</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8159</v>
+        <v>-1.9604</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5147</v>
+        <v>-0.5789</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3011</v>
+        <v>-1.3815</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8072</v>
+        <v>-1.5007</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.889</v>
+        <v>-0.586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9182</v>
+        <v>-0.9146</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.211000000000001</v>
+        <v>2.559200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>8.2272</v>
+        <v>10.6009</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.016100000000001</v>
+        <v>-8.041699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.135200000000003</v>
+        <v>1.053000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>17.7423</v>
+        <v>17.9937</v>
       </c>
       <c r="I14" t="n">
-        <v>-16.6072</v>
+        <v>-16.9406</v>
       </c>
       <c r="J14" t="n">
-        <v>12.5827</v>
+        <v>13.92</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8223</v>
+        <v>17.7431</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.2394</v>
+        <v>-3.823</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.4476</v>
+        <v>-12.867</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9199999999999998</v>
+        <v>0.2507</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.3676</v>
+        <v>-13.1176</v>
       </c>
       <c r="P14" t="n">
-        <v>8.002300000000002</v>
+        <v>7.789500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.0032</v>
+        <v>-10.7105</v>
       </c>
       <c r="R14" t="n">
-        <v>19.0055</v>
+        <v>18.5</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.4251</v>
+        <v>-8.9017</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7904999999999995</v>
+        <v>1.2646</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.2156</v>
+        <v>-10.1662</v>
       </c>
       <c r="V14" t="n">
-        <v>2.498800000000001</v>
+        <v>2.6184</v>
       </c>
       <c r="W14" t="n">
-        <v>5.8572</v>
+        <v>6.1269</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.3584</v>
+        <v>-3.5084</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4269</v>
+        <v>2.9719</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0406</v>
+        <v>4.9112</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6137</v>
+        <v>-1.9393</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9663</v>
+        <v>1.9947</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3171</v>
+        <v>-1.3773</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2833</v>
+        <v>3.372</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0323</v>
+        <v>4.2827</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5832</v>
+        <v>1.6884</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4492</v>
+        <v>2.5943</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0661</v>
+        <v>-2.288</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.9002</v>
+        <v>-3.0657</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S15" t="n">
-        <v>1.801</v>
+        <v>1.2819</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0297</v>
+        <v>1.5164</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2287</v>
+        <v>-0.2344</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3846</v>
+        <v>2.6839</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0613</v>
+        <v>2.4721</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3233</v>
+        <v>0.2118</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5978</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3181</v>
+        <v>0.2171</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2797</v>
+        <v>-0.7408</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6414</v>
+        <v>0.467</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6398</v>
+        <v>1.5934</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0016</v>
+        <v>-1.1264</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0437</v>
+        <v>-0.9907</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3217</v>
+        <v>-1.3763</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2781</v>
+        <v>0.3856</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0131</v>
+        <v>2.0129</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4202</v>
+        <v>1.3945</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4333</v>
+        <v>0.6183</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3425</v>
+        <v>2.6632</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2768</v>
+        <v>0.9482</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06569999999999999</v>
+        <v>1.715</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5425</v>
+        <v>3.035</v>
       </c>
       <c r="H17" t="n">
-        <v>0.193</v>
+        <v>0.1642</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7355</v>
+        <v>2.8708</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3653</v>
+        <v>2.6362</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5214</v>
+        <v>0.6826</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.156</v>
+        <v>1.9536</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.3988</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3283</v>
+        <v>-0.5184</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4205</v>
+        <v>0.9172</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6002</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6002</v>
+        <v>1.1684</v>
       </c>
       <c r="S17" t="n">
-        <v>1.685</v>
+        <v>0.5503</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3116</v>
+        <v>0.4541</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3734</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5999</v>
+        <v>0.0516</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7996</v>
+        <v>2.4784</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7996</v>
+        <v>2.1511</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.3273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7996</v>
+        <v>2.605</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1997</v>
+        <v>0.295</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5999</v>
+        <v>2.31</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7996</v>
+        <v>2.7076</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1997</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5999</v>
+        <v>2.0508</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.1026</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.3618</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.2592</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.4172</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7362</v>
+        <v>1.8395</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4871</v>
+        <v>1.8395</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2233</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.0064</v>
+        <v>1.8395</v>
       </c>
       <c r="H19" t="n">
-        <v>0.16</v>
+        <v>1.2316</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8465</v>
+        <v>0.6079</v>
       </c>
       <c r="J19" t="n">
-        <v>2.487</v>
+        <v>1.8395</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6034</v>
+        <v>1.2316</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8835</v>
+        <v>0.6079</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5194</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4435</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9629</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3502</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7735</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4232</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8026</v>
+        <v>1.4949</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1214</v>
+        <v>1.7893</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3188</v>
+        <v>-0.2945</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7931</v>
+        <v>0.8097</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1022</v>
+        <v>-1.1063</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8953</v>
+        <v>1.9161</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2436</v>
+        <v>1.3057</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4505</v>
+        <v>-0.496</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1289</v>
+        <v>0.8546</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1222</v>
+        <v>0.4836</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2511</v>
+        <v>0.371</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3127</v>
+        <v>0.1097</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6367</v>
+        <v>0.5608</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3239</v>
+        <v>-0.4511</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5948</v>
+        <v>-2.665</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.8327</v>
+        <v>-3.8969</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2379</v>
+        <v>1.2319</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2275</v>
+        <v>0.3309</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2542</v>
+        <v>-1.193</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4817</v>
+        <v>1.5239</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8223</v>
+        <v>-2.9959</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5785</v>
+        <v>-2.7039</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S21" t="n">
-        <v>2.0273</v>
+        <v>1.9178</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8096</v>
+        <v>1.593</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2177</v>
+        <v>0.3249</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2113</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6317</v>
+        <v>-1.4798</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4204</v>
+        <v>1.5615</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7893</v>
+        <v>0.764</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4937</v>
+        <v>0.469</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2956</v>
+        <v>0.295</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.438</v>
+        <v>-0.4203</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.518</v>
+        <v>-0.5024</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2273</v>
+        <v>1.1843</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4137</v>
+        <v>0.3869</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8136</v>
+        <v>0.7974</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6004</v>
+        <v>-0.2928</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1934</v>
+        <v>-0.0858</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.407</v>
+        <v>-0.207</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2418</v>
+        <v>-0.9431</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2141</v>
+        <v>0.0002</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4559</v>
+        <v>-0.9433</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5672</v>
+        <v>-0.7416</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1729</v>
+        <v>-1.2542</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3942</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5447</v>
+        <v>-0.0838</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9943</v>
+        <v>0.0616</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5504</v>
+        <v>-0.1454</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0225</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1786</v>
+        <v>-1.3158</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1562</v>
+        <v>0.6579</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2003</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5248</v>
+        <v>-0.1167</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9589</v>
+        <v>0.2787</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.434</v>
+        <v>-0.3955</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1998</v>
+        <v>-0.2795</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1998</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0371</v>
+        <v>-1.1944</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.017</v>
+        <v>1.4816</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0201</v>
+        <v>-2.676</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7446</v>
+        <v>0.1657</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1971</v>
+        <v>-2.7992</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4525</v>
+        <v>2.965</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1724</v>
+        <v>3.2762</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06</v>
+        <v>0.0257</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2324</v>
+        <v>3.2505</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5722</v>
+        <v>-3.1105</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2571</v>
+        <v>-2.825</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6849</v>
+        <v>-0.2855</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2001</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2001</v>
+        <v>-3.1158</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2328</v>
+        <v>0.7819</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6446</v>
+        <v>0.7107</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5881999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2598</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.342</v>
+        <v>-2.8067</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4238</v>
+        <v>-0.2435</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7658</v>
+        <v>-2.5632</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1553</v>
+        <v>-3.5515</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.7574</v>
+        <v>-3.2195</v>
       </c>
       <c r="I25" t="n">
-        <v>2.9127</v>
+        <v>-0.3319</v>
       </c>
       <c r="J25" t="n">
-        <v>3.127</v>
+        <v>-1.3713</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0364</v>
+        <v>-0.9261</v>
       </c>
       <c r="L25" t="n">
-        <v>3.1634</v>
+        <v>-0.4452</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.9717</v>
+        <v>-2.1802</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.721</v>
+        <v>-2.2934</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2506</v>
+        <v>0.1132</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2006</v>
+        <v>0.9737</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.2009</v>
+        <v>-0.1947</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2967</v>
+        <v>0.9921</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1022</v>
+        <v>1.3226</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1946</v>
+        <v>-0.3304</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5999</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4081</v>
+        <v>-3.6502</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7647</v>
+        <v>-3.0098</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6434</v>
+        <v>-0.6405</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.3314</v>
+        <v>-1.3177</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.3936</v>
+        <v>-3.3893</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0622</v>
+        <v>2.0716</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3693</v>
+        <v>0.5006</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6723</v>
+        <v>-1.5907</v>
       </c>
       <c r="L26" t="n">
-        <v>2.0416</v>
+        <v>2.0913</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.7007</v>
+        <v>-1.8183</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.7213</v>
+        <v>-1.7987</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.4013</v>
+        <v>-4.2842</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>3.745</v>
+        <v>2.3343</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2878</v>
+        <v>1.7406</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4572</v>
+        <v>0.5937</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.7757</v>
+        <v>-6.6498</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.8574</v>
+        <v>-4.6004</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.9183</v>
+        <v>-2.0494</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.4624</v>
+        <v>-3.4672</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.3336</v>
+        <v>-3.3277</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.6902</v>
+        <v>-2.6041</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.0122</v>
+        <v>-1.9396</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.7722</v>
+        <v>-0.8631</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.3214</v>
+        <v>-1.3881</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0064</v>
+        <v>0.1553</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2335</v>
+        <v>0.3406</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.227</v>
+        <v>-0.1853</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="28">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.210900000000001</v>
+        <v>-0.9209999999999985</v>
       </c>
       <c r="E28" t="n">
-        <v>4.816400000000002</v>
+        <v>6.8205</v>
       </c>
       <c r="F28" t="n">
-        <v>-7.027199999999999</v>
+        <v>-7.7417</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.135100000000001</v>
+        <v>-1.0531</v>
       </c>
       <c r="H28" t="n">
-        <v>-17.7421</v>
+        <v>-17.9935</v>
       </c>
       <c r="I28" t="n">
-        <v>16.6072</v>
+        <v>16.9407</v>
       </c>
       <c r="J28" t="n">
-        <v>11.4477</v>
+        <v>12.8669</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.9199000000000002</v>
+        <v>-0.2506999999999997</v>
       </c>
       <c r="L28" t="n">
-        <v>12.3677</v>
+        <v>13.1176</v>
       </c>
       <c r="M28" t="n">
-        <v>-12.583</v>
+        <v>-13.92</v>
       </c>
       <c r="N28" t="n">
-        <v>-16.8221</v>
+        <v>-17.7431</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2396</v>
+        <v>3.822900000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>-8.0023</v>
+        <v>-7.7895</v>
       </c>
       <c r="Q28" t="n">
-        <v>-19.0055</v>
+        <v>-18.4999</v>
       </c>
       <c r="R28" t="n">
-        <v>11.0031</v>
+        <v>10.7104</v>
       </c>
       <c r="S28" t="n">
-        <v>9.425199999999998</v>
+        <v>10.5397</v>
       </c>
       <c r="T28" t="n">
-        <v>10.2154</v>
+        <v>10.1662</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.7901999999999999</v>
+        <v>0.3736999999999998</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.4988</v>
+        <v>-2.6185</v>
       </c>
       <c r="W28" t="n">
-        <v>2.1587</v>
+        <v>2.2874</v>
       </c>
       <c r="X28" t="n">
-        <v>-4.6575</v>
+        <v>-4.9059</v>
       </c>
     </row>
   </sheetData>
